--- a/master/result/51_秋天遇见你_校园恋曲/51_秋天遇见你_校园恋曲.xlsx
+++ b/master/result/51_秋天遇见你_校园恋曲/51_秋天遇见你_校园恋曲.xlsx
@@ -397,302 +397,381 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:D26"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="8.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文含义</v>
+        <v>词性</v>
+      </c>
+      <c r="D1" t="str">
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>lonely</v>
       </c>
       <c r="B2" t="str">
-        <v>lonely</v>
+        <v>/lonely/</v>
       </c>
       <c r="C2" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>孤独的</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>textbook</v>
       </c>
       <c r="B3" t="str">
-        <v>textbook</v>
+        <v>/textbook/</v>
       </c>
       <c r="C3" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>教科书</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>brown</v>
       </c>
       <c r="B4" t="str">
-        <v>brown</v>
+        <v>/brown/</v>
       </c>
       <c r="C4" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>棕色</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>splash</v>
       </c>
       <c r="B5" t="str">
-        <v>splash</v>
+        <v>/splash/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>溅</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>when</v>
       </c>
       <c r="B6" t="str">
-        <v>when</v>
+        <v>/when/</v>
       </c>
       <c r="C6" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D6" t="str">
         <v>何时</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>symphony</v>
       </c>
       <c r="B7" t="str">
-        <v>symphony</v>
+        <v>/symphony/</v>
       </c>
       <c r="C7" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>交响乐</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>composition</v>
       </c>
       <c r="B8" t="str">
-        <v>composition</v>
+        <v>/ˌkɒmpəˈzɪʃn/</v>
       </c>
       <c r="C8" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D8" t="str">
         <v>作文</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>able</v>
       </c>
       <c r="B9" t="str">
-        <v>able</v>
+        <v>/ˈeɪbəl/</v>
       </c>
       <c r="C9" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D9" t="str">
         <v>有能力的</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>condense</v>
       </c>
       <c r="B10" t="str">
-        <v>condense</v>
+        <v>/condense/</v>
       </c>
       <c r="C10" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>浓缩</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>miracle</v>
       </c>
       <c r="B11" t="str">
-        <v>miracle</v>
+        <v>/miracle/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>奇迹</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>autumn</v>
       </c>
       <c r="B12" t="str">
-        <v>autumn</v>
+        <v>/autumn/</v>
       </c>
       <c r="C12" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>秋天</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>northwest</v>
       </c>
       <c r="B13" t="str">
-        <v>northwest</v>
+        <v>/northwest/</v>
       </c>
       <c r="C13" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D13" t="str">
         <v>西北</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>baggage</v>
       </c>
       <c r="B14" t="str">
-        <v>baggage</v>
+        <v>/ˈbæɡɪdʒ/</v>
       </c>
       <c r="C14" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D14" t="str">
         <v>行李</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>kit</v>
       </c>
       <c r="B15" t="str">
-        <v>kit</v>
+        <v>/kit/</v>
       </c>
       <c r="C15" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>工具箱</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>delicious</v>
       </c>
       <c r="B16" t="str">
-        <v>delicious</v>
+        <v>/delicious/</v>
       </c>
       <c r="C16" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D16" t="str">
         <v>美味的</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>combine</v>
       </c>
       <c r="B17" t="str">
-        <v>combine</v>
+        <v>/kəmˈbaɪn/</v>
       </c>
       <c r="C17" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>联合</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>blanket</v>
       </c>
       <c r="B18" t="str">
-        <v>blanket</v>
+        <v>/ˈblæŋkɪt/</v>
       </c>
       <c r="C18" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>毯子</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>fabric</v>
       </c>
       <c r="B19" t="str">
-        <v>fabric</v>
+        <v>/fabric/</v>
       </c>
       <c r="C19" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>织物</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>hug</v>
       </c>
       <c r="B20" t="str">
-        <v>hug</v>
+        <v>/hug/</v>
       </c>
       <c r="C20" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>拥抱</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>merry</v>
       </c>
       <c r="B21" t="str">
-        <v>merry</v>
+        <v>/merry/</v>
       </c>
       <c r="C21" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>愉快的</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>skate</v>
       </c>
       <c r="B22" t="str">
-        <v>skate</v>
+        <v>/skeɪt/</v>
       </c>
       <c r="C22" t="str">
+        <v>v.</v>
+      </c>
+      <c r="D22" t="str">
         <v>冰鞋</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>roast</v>
       </c>
       <c r="B23" t="str">
-        <v>roast</v>
+        <v>/roast/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D23" t="str">
         <v>烤</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>ambitious</v>
       </c>
       <c r="B24" t="str">
-        <v>ambitious</v>
+        <v>/ambitious/</v>
       </c>
       <c r="C24" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D24" t="str">
         <v>有抱负的</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>powerful</v>
       </c>
       <c r="B25" t="str">
-        <v>powerful</v>
+        <v>/powerful/</v>
       </c>
       <c r="C25" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D25" t="str">
         <v>强大的</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>boil</v>
       </c>
       <c r="B26" t="str">
-        <v>boil</v>
+        <v>/bɔɪl/</v>
       </c>
       <c r="C26" t="str">
+        <v>v./n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>沸腾</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C26"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D26"/>
   </ignoredErrors>
 </worksheet>
 </file>